--- a/datos/EXTRACTORES_COMPLETO.xlsx
+++ b/datos/EXTRACTORES_COMPLETO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_ARCHIVOS\TRABAJO\Facturas\ParsearFacturas-main\datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_ARCHIVOS\TRABAJO\Facturas\gestion-facturas\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7EF1CF-A647-45BB-ACBE-812CE349F6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DC327F-1E72-495A-8C8B-EBC75C40827B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1167,16 +1167,16 @@
   <dxfs count="3">
     <dxf>
       <border outline="0">
-        <bottom style="thin">
+        <top style="thin">
           <color auto="1"/>
-        </bottom>
+        </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
-        <top style="thin">
+        <bottom style="thin">
           <color auto="1"/>
-        </top>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1222,14 +1222,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{370F3B05-5D41-432D-A8F2-1CEA88B61F97}" name="Tabla1" displayName="Tabla1" ref="A1:H94" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="0" tableBorderDxfId="1">
-  <autoFilter ref="A1:H94" xr:uid="{370F3B05-5D41-432D-A8F2-1CEA88B61F97}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="JAMONES BERNAL"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{370F3B05-5D41-432D-A8F2-1CEA88B61F97}" name="Tabla1" displayName="Tabla1" ref="A1:H94" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="A1:H94" xr:uid="{370F3B05-5D41-432D-A8F2-1CEA88B61F97}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H92">
     <sortCondition ref="A4:A92"/>
   </sortState>
@@ -1572,7 +1566,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1598,7 +1592,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1624,7 +1618,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>90</v>
       </c>
@@ -1644,7 +1638,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>91</v>
       </c>
@@ -1664,7 +1658,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1684,7 +1678,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1704,7 +1698,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1727,7 +1721,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1750,7 +1744,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1770,7 +1764,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1790,7 +1784,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1810,7 +1804,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1830,7 +1824,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1850,7 +1844,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1870,7 +1864,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>92</v>
       </c>
@@ -1887,7 +1881,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -1907,7 +1901,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1927,7 +1921,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1947,7 +1941,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1970,7 +1964,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>93</v>
       </c>
@@ -1987,7 +1981,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -2007,7 +2001,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -2030,7 +2024,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -2053,7 +2047,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -2073,7 +2067,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -2093,7 +2087,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -2113,7 +2107,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>94</v>
       </c>
@@ -2130,7 +2124,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -2150,7 +2144,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -2170,7 +2164,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -2190,7 +2184,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -2213,7 +2207,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -2233,7 +2227,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -2253,7 +2247,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -2273,7 +2267,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -2296,7 +2290,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -2319,7 +2313,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -2342,7 +2336,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -2362,7 +2356,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -2385,7 +2379,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -2405,7 +2399,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -2448,7 +2442,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>45</v>
       </c>
@@ -2465,7 +2459,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -2488,7 +2482,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -2511,7 +2505,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -2531,7 +2525,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>49</v>
       </c>
@@ -2554,7 +2548,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -2574,7 +2568,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -2594,7 +2588,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -2617,7 +2611,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -2637,7 +2631,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>54</v>
       </c>
@@ -2657,7 +2651,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>55</v>
       </c>
@@ -2680,7 +2674,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>95</v>
       </c>
@@ -2697,7 +2691,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>56</v>
       </c>
@@ -2720,7 +2714,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>57</v>
       </c>
@@ -2743,7 +2737,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -2766,7 +2760,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>59</v>
       </c>
@@ -2786,7 +2780,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>96</v>
       </c>
@@ -2803,7 +2797,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -2823,7 +2817,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -2843,7 +2837,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -2863,7 +2857,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>63</v>
       </c>
@@ -2883,7 +2877,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>64</v>
       </c>
@@ -2906,7 +2900,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>65</v>
       </c>
@@ -2929,7 +2923,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -2952,7 +2946,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>67</v>
       </c>
@@ -2975,7 +2969,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>97</v>
       </c>
@@ -2992,7 +2986,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>68</v>
       </c>
@@ -3012,7 +3006,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>69</v>
       </c>
@@ -3035,7 +3029,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>70</v>
       </c>
@@ -3055,7 +3049,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>71</v>
       </c>
@@ -3081,7 +3075,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>72</v>
       </c>
@@ -3101,7 +3095,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>73</v>
       </c>
@@ -3121,7 +3115,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>74</v>
       </c>
@@ -3141,7 +3135,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>75</v>
       </c>
@@ -3161,7 +3155,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>98</v>
       </c>
@@ -3178,7 +3172,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>76</v>
       </c>
@@ -3198,7 +3192,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>77</v>
       </c>
@@ -3221,7 +3215,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>78</v>
       </c>
@@ -3244,7 +3238,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>79</v>
       </c>
@@ -3264,7 +3258,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>80</v>
       </c>
@@ -3287,7 +3281,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>81</v>
       </c>
@@ -3310,7 +3304,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>82</v>
       </c>
@@ -3330,7 +3324,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>83</v>
       </c>
@@ -3353,7 +3347,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>84</v>
       </c>
@@ -3373,7 +3367,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>85</v>
       </c>
@@ -3393,7 +3387,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>86</v>
       </c>
@@ -3416,7 +3410,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>87</v>
       </c>
@@ -3439,7 +3433,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>88</v>
       </c>
@@ -3462,7 +3456,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>89</v>
       </c>
@@ -3482,7 +3476,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>353</v>
       </c>
